--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N5_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N5_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>55.3629365594397</v>
+        <v>8.996477190908951</v>
       </c>
       <c r="D2" t="n">
-        <v>55.31875069186229</v>
+        <v>8.989296987427622</v>
       </c>
       <c r="E2" t="n">
-        <v>4.539871619306754</v>
+        <v>0.7377291381373474</v>
       </c>
       <c r="F2" t="n">
-        <v>3.741744038198727</v>
+        <v>0.6080334062072931</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>55.61809506276739</v>
+        <v>9.0379404476997</v>
       </c>
       <c r="D3" t="n">
-        <v>54.25381499199173</v>
+        <v>8.816244936198657</v>
       </c>
       <c r="E3" t="n">
-        <v>4.539871619306754</v>
+        <v>0.7377291381373474</v>
       </c>
       <c r="F3" t="n">
-        <v>3.741744038198727</v>
+        <v>0.6080334062072931</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>44.86785932458663</v>
+        <v>7.291027140245327</v>
       </c>
       <c r="D4" t="n">
-        <v>46.2415566816604</v>
+        <v>7.514252960769815</v>
       </c>
       <c r="E4" t="n">
-        <v>4.539871619306754</v>
+        <v>0.7377291381373474</v>
       </c>
       <c r="F4" t="n">
-        <v>3.741744038198727</v>
+        <v>0.6080334062072931</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>48.85512684556285</v>
+        <v>7.938958112403964</v>
       </c>
       <c r="D5" t="n">
-        <v>48.93567438895549</v>
+        <v>7.952047088205267</v>
       </c>
       <c r="E5" t="n">
-        <v>4.539871619306754</v>
+        <v>0.7377291381373474</v>
       </c>
       <c r="F5" t="n">
-        <v>3.741744038198727</v>
+        <v>0.6080334062072931</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
